--- a/content/text-lists.xlsx
+++ b/content/text-lists.xlsx
@@ -1,41 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinhchan\Desktop\dunglook\dunglook-generator\content\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE5CD1B-3DB7-4ACD-A002-DF8D70C790E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="texts" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>suffix</t>
+  </si>
+  <si>
+    <t>Tan làm</t>
+  </si>
+  <si>
+    <t>tắc đường</t>
+  </si>
+  <si>
+    <t>Điện thoại hết pin</t>
+  </si>
+  <si>
+    <t>ra ngoài</t>
+  </si>
+  <si>
+    <t>Buồn ỉa</t>
+  </si>
+  <si>
+    <t>đi chơi</t>
+  </si>
+  <si>
+    <t>Trúng số</t>
+  </si>
+  <si>
+    <t>đi tù</t>
+  </si>
+  <si>
+    <t>Trốn thuế</t>
+  </si>
+  <si>
+    <t>thanh tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Được tăng lương </t>
+  </si>
+  <si>
+    <t>xin nghỉ</t>
+  </si>
+  <si>
+    <t>Khóc</t>
+  </si>
+  <si>
+    <t>cười</t>
+  </si>
+  <si>
+    <t>Ngủ quên</t>
+  </si>
+  <si>
+    <t>đi họp</t>
+  </si>
+  <si>
+    <t>Tăng ca</t>
+  </si>
+  <si>
+    <t>tan ca</t>
+  </si>
+  <si>
+    <t>Đi date</t>
+  </si>
+  <si>
+    <t>chưa muốn yêu</t>
+  </si>
+  <si>
+    <t>Lương về</t>
+  </si>
+  <si>
+    <t>trả nợ</t>
+  </si>
+  <si>
+    <t>Xinh đẹp</t>
+  </si>
+  <si>
+    <t>xấu xí</t>
+  </si>
+  <si>
+    <t>Trời đánh</t>
+  </si>
+  <si>
+    <t>bữa ăn</t>
+  </si>
+  <si>
+    <t>Tiết lộ</t>
+  </si>
+  <si>
+    <t>đéo cần</t>
+  </si>
+  <si>
+    <t>Thông minh</t>
+  </si>
+  <si>
+    <t>Ngu</t>
+  </si>
+  <si>
+    <t>thông minh</t>
+  </si>
+  <si>
+    <t>ngu</t>
+  </si>
+  <si>
+    <t>Cười</t>
+  </si>
+  <si>
+    <t>khóc</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +164,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,76 +503,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="31.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>prefix</v>
-      </c>
-      <c r="B1" t="str">
-        <v>suffix</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Hôm nay tôi</v>
-      </c>
-      <c r="B2" t="str">
-        <v>quá xịn!</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Cứ phải là</v>
-      </c>
-      <c r="B3" t="str">
-        <v>cực phẩm!</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Sáng nay</v>
-      </c>
-      <c r="B4" t="str">
-        <v>siêu cool</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Một ngày</v>
-      </c>
-      <c r="B5" t="str">
-        <v>đỉnh nóc</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Đi đâu cũng</v>
-      </c>
-      <c r="B6" t="str">
-        <v>chuẩn bài</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Look hôm nay</v>
-      </c>
-      <c r="B7" t="str">
-        <v>trendy AF</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Nhìn là biết</v>
-      </c>
-      <c r="B8" t="str">
-        <v>gu cực mạnh</v>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
+    <ignoredError sqref="A1:B1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/content/text-lists.xlsx
+++ b/content/text-lists.xlsx
@@ -1,140 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dinhchan\Desktop\dunglook\dunglook-generator\content\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE5CD1B-3DB7-4ACD-A002-DF8D70C790E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="texts" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>prefix</t>
-  </si>
-  <si>
-    <t>suffix</t>
-  </si>
-  <si>
-    <t>Tan làm</t>
-  </si>
-  <si>
-    <t>tắc đường</t>
-  </si>
-  <si>
-    <t>Điện thoại hết pin</t>
-  </si>
-  <si>
-    <t>ra ngoài</t>
-  </si>
-  <si>
-    <t>Buồn ỉa</t>
-  </si>
-  <si>
-    <t>đi chơi</t>
-  </si>
-  <si>
-    <t>Trúng số</t>
-  </si>
-  <si>
-    <t>đi tù</t>
-  </si>
-  <si>
-    <t>Trốn thuế</t>
-  </si>
-  <si>
-    <t>thanh tra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Được tăng lương </t>
-  </si>
-  <si>
-    <t>xin nghỉ</t>
-  </si>
-  <si>
-    <t>Khóc</t>
-  </si>
-  <si>
-    <t>cười</t>
-  </si>
-  <si>
-    <t>Ngủ quên</t>
-  </si>
-  <si>
-    <t>đi họp</t>
-  </si>
-  <si>
-    <t>Tăng ca</t>
-  </si>
-  <si>
-    <t>tan ca</t>
-  </si>
-  <si>
-    <t>Đi date</t>
-  </si>
-  <si>
-    <t>chưa muốn yêu</t>
-  </si>
-  <si>
-    <t>Lương về</t>
-  </si>
-  <si>
-    <t>trả nợ</t>
-  </si>
-  <si>
-    <t>Xinh đẹp</t>
-  </si>
-  <si>
-    <t>xấu xí</t>
-  </si>
-  <si>
-    <t>Trời đánh</t>
-  </si>
-  <si>
-    <t>bữa ăn</t>
-  </si>
-  <si>
-    <t>Tiết lộ</t>
-  </si>
-  <si>
-    <t>đéo cần</t>
-  </si>
-  <si>
-    <t>Thông minh</t>
-  </si>
-  <si>
-    <t>Ngu</t>
-  </si>
-  <si>
-    <t>thông minh</t>
-  </si>
-  <si>
-    <t>ngu</t>
-  </si>
-  <si>
-    <t>Cười</t>
-  </si>
-  <si>
-    <t>khóc</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -164,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -503,162 +396,424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C37"/>
   <cols>
-    <col min="1" max="1" width="20.75" customWidth="1"/>
-    <col min="2" max="2" width="31.75" customWidth="1"/>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>topic</v>
+      </c>
+      <c r="B1" t="str">
+        <v>prefix</v>
+      </c>
+      <c r="C1" t="str">
+        <v>suffix</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Trời mưa</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Đi làm</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Trời nắng</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Trà đá</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Mưa rào</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Gội đầu</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Trời nóng</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Hỏng điều hoà</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Sáng nắng chiều mưa</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Khó ở</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Nắng đẹp</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Sống ảo</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Thời tiết</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Gió mùa về</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Không có người yêu</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Matcha</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Mát mẻ</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Cà phê</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Buồn ngủ</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Trà sữa</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Gồng deadline</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Ăn lẩu</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Trời lạnh</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Mì tôm</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Cuối tháng</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Về nhà ăn cơm</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Hết tiền</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Bánh ngọt</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Tụt mood</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Salad</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Healthy</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Thèm gà rán</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Cheatday</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Trà đá</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Chán chường</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Crush thích mình</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Mình không thích họ nữa</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Người yêu cũ nhắn tin</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Đang ổn</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Chia tay người yêu</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Bạn bè cưới hết</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Không muốn yêu</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Greenflag xuất hiện</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Lên đồ lồng lộn</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Huỷ kèo</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Tăng ca</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Tan ca</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Thang máy hỏng</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Đang vội</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Hỏng máy</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Deadline</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Trả nợ</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Nhận lương</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Huỷ kèo</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Mặc đẹp</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Sale-off</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Định tiết kiệm</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Những tình huống tréo ngoe</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Khách đổi brief</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Final</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Vấn đề thời sự</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Xăng tăng</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Định đổ xăng</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Đi ăn</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Đi uống</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Đi chơi</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Đi làm</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Đi picnic</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Đi hội</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B1" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/content/text-lists.xlsx
+++ b/content/text-lists.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="texts" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,12 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -494,326 +489,1030 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B9" t="str">
-        <v>Matcha</v>
+        <v>Bão bùng</v>
       </c>
       <c r="C9" t="str">
-        <v>Mát mẻ</v>
+        <v>Đi chơi</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B10" t="str">
-        <v>Cà phê</v>
+        <v>Giở giời</v>
       </c>
       <c r="C10" t="str">
-        <v>Buồn ngủ</v>
+        <v>Vi vu</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B11" t="str">
-        <v>Trà sữa</v>
+        <v>Âm u</v>
       </c>
       <c r="C11" t="str">
-        <v>Gồng deadline</v>
+        <v>Du lịch</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B12" t="str">
-        <v>Ăn lẩu</v>
+        <v>Sấm chớp</v>
       </c>
       <c r="C12" t="str">
-        <v>Trời lạnh</v>
+        <v>Lượn đường</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B13" t="str">
-        <v>Mì tôm</v>
+        <v>Nồm</v>
       </c>
       <c r="C13" t="str">
-        <v>Cuối tháng</v>
+        <v>Chia tay</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B14" t="str">
-        <v>Về nhà ăn cơm</v>
+        <v>Dịu keo</v>
       </c>
       <c r="C14" t="str">
-        <v>Hết tiền</v>
+        <v>Tỏ tình</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B15" t="str">
-        <v>Bánh ngọt</v>
+        <v>Chill chill</v>
       </c>
       <c r="C15" t="str">
-        <v>Tụt mood</v>
+        <v>Chốt deal</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B16" t="str">
-        <v>Salad</v>
+        <v>Giông tố</v>
       </c>
       <c r="C16" t="str">
-        <v>Healthy</v>
+        <v>Đi quẩy</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B17" t="str">
-        <v>Thèm gà rán</v>
+        <v>Hoàng hôn</v>
       </c>
       <c r="C17" t="str">
-        <v>Cheatday</v>
+        <v>Ngồi chill</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Đồ ăn, đồ uống</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B18" t="str">
-        <v>Trà đá</v>
+        <v>Bình minh</v>
       </c>
       <c r="C18" t="str">
-        <v>Chán chường</v>
+        <v>Không làm gì</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Tình yêu</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B19" t="str">
-        <v>Crush thích mình</v>
+        <v>Mưa gió</v>
       </c>
       <c r="C19" t="str">
-        <v>Mình không thích họ nữa</v>
+        <v>Hỏng xe</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Tình yêu</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B20" t="str">
-        <v>Người yêu cũ nhắn tin</v>
+        <v>Nắng cực đại</v>
       </c>
       <c r="C20" t="str">
-        <v>Đang ổn</v>
+        <v>Hết xăng</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Tình yêu</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B21" t="str">
-        <v>Chia tay người yêu</v>
+        <v>Mưa cực to</v>
       </c>
       <c r="C21" t="str">
-        <v>Bạn bè cưới hết</v>
+        <v>Ăn sáng</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Tình yêu</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B22" t="str">
-        <v>Không muốn yêu</v>
+        <v>Bụi mù</v>
       </c>
       <c r="C22" t="str">
-        <v>Greenflag xuất hiện</v>
+        <v>Ngã xe</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Tình yêu</v>
+        <v>Thời tiết</v>
       </c>
       <c r="B23" t="str">
-        <v>Lên đồ lồng lộn</v>
+        <v>Thiên thạch rơi</v>
       </c>
       <c r="C23" t="str">
-        <v>Huỷ kèo</v>
+        <v>Nhặt được tiền</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B24" t="str">
-        <v>Tăng ca</v>
+        <v>Matcha</v>
       </c>
       <c r="C24" t="str">
-        <v>Tan ca</v>
+        <v>Mát mẻ</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B25" t="str">
-        <v>Thang máy hỏng</v>
+        <v>Cà phê</v>
       </c>
       <c r="C25" t="str">
-        <v>Đang vội</v>
+        <v>Mất ngủ</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B26" t="str">
-        <v>Hỏng máy</v>
+        <v>Trà sữa</v>
       </c>
       <c r="C26" t="str">
-        <v>Deadline</v>
+        <v>Gồng deadline</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B27" t="str">
-        <v>Trả nợ</v>
+        <v>Ăn lẩu</v>
       </c>
       <c r="C27" t="str">
-        <v>Nhận lương</v>
+        <v>Trời lạnh</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B28" t="str">
-        <v>Huỷ kèo</v>
+        <v>Mì tôm</v>
       </c>
       <c r="C28" t="str">
-        <v>Mặc đẹp</v>
+        <v>Cuối tháng</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B29" t="str">
-        <v>Sale-off</v>
+        <v>Về nhà ăn cơm</v>
       </c>
       <c r="C29" t="str">
-        <v>Định tiết kiệm</v>
+        <v>Hết tiền</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Những tình huống tréo ngoe</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B30" t="str">
-        <v>Khách đổi brief</v>
+        <v>Ăn bánh ngọt</v>
       </c>
       <c r="C30" t="str">
-        <v>Final</v>
+        <v>Tụt mood</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Vấn đề thời sự</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B31" t="str">
-        <v>Xăng tăng</v>
+        <v>Ăn salad</v>
       </c>
       <c r="C31" t="str">
-        <v>Định đổ xăng</v>
+        <v>Healthy</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Đi đâu</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B32" t="str">
-        <v>Đi ăn</v>
+        <v>Thèm gà rán</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>Cheatday</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Đi đâu</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B33" t="str">
-        <v>Đi uống</v>
+        <v>Trà đá</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>Chán chường</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Đi đâu</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B34" t="str">
-        <v>Đi chơi</v>
+        <v>Ăn khiêng</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>Bồ đá</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Đi đâu</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B35" t="str">
-        <v>Đi làm</v>
+        <v>Nhịn đói</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>No bụng</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Đi đâu</v>
+        <v>Đồ ăn, đồ uống</v>
       </c>
       <c r="B36" t="str">
-        <v>Đi picnic</v>
+        <v>Xiên bẩn</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>Đói meo</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Pizza</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Say sưa</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Detox</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Hoa mắt chóng mặt</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Thèm cơm</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Tụt huyết áp</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Thèm phở</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Tiểu đường</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Chán cơm</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Ốm đau</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Phở bò</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Chán ăn</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Omakase</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Trúng số</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Đồ ăn, đồ uống</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Fine Dining</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Quẩy bar</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Crush thích mình</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Mình không thích họ nữa</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Người yêu cũ nhắn tin</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Đang ổn</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Chia tay người yêu</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Bạn bè cưới hết</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Không muốn yêu</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Greenflag xuất hiện</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Lên đồ lồng lộn</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Bị huỷ kèo</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Đơn phương</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Gặp Red Flag</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Thành lốp trưởng</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Gặp cạ</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Loạn nhịp</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Đang có người yêu</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Ghen</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Tình cảm đậm sâu</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Ỡm ờ</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Chán yêu</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Thả thính</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Lười yêu</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Dính thính</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Xiêu lòng</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Đi date</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Yêu thương sâu đậm</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Thích mập mờ</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Cringe</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Bị làm quen</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Xấu xí</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Đong đưa</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Siêu xinh</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Nhớ người yêu cũ</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Chưa quên người cũ</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Dỗi hờn</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Gặp may</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Tình yêu</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Bắt cá hai tay</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Cô đơn</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Tăng ca</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Tan ca</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Tắc đường</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Đang vội</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Hỏng máy</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Deadline</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Trả nợ</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Nhận lương</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Huỷ kèo</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Mặc đẹp</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Sale-off</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Hết tiền</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Khách đổi brief</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Xuất file</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Điện thoại hết pin</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Nhớ người yêu</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Đi phượt</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Nhớ nhà</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Muốn chill</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Bị dí</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Yêu đời</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Chán đời</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Thông minh đột xuất</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Cô đơn</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Bị ốm</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Ngẫn ngờ</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Bồ đá</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Phê pha</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Xe hỏng</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Trúng Vietlot</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Mất ngủ</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Buồn ngủ</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Tréo ngoe</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Đau bụng</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Buồn ẻ</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Học bài</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Đi tắm</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Trúng tủ</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Đi thi</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Chăm chỉ</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Cúp học</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Thuộc bài</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Vào lớp</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Học bổng</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Ra chơi</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Ôn tập</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Tan trường</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Quên bài</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Về nhà</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Thần đồng</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Thức khua</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Tỉnh táo</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Đi chơi</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Học hành</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Ngủ gật</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Kiểm tra</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
         <v>Đi đâu</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B91" t="str">
+        <v>Đi ăn</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Xe hết xăng</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Đi uống</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Bị ốm</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Đi chơi</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Xinh đẹp</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Đi làm</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Nhiều tiền</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Đi lượn</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Rảnh háng</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B96" t="str">
         <v>Đi hội</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C96" t="str">
+        <v>Bận ơi là bận</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Đi quẩy</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Nhà bao việc</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Đi tiệc</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Không có gì làm</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Đi đâu</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Đi học</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Xấu điên</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Bợ</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Chọn trường</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Đến Swinburne</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Bợ</v>
+      </c>
+      <c r="B101" t="str">
         <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>Hội thảo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C101"/>
   </ignoredErrors>
 </worksheet>
 </file>